--- a/Base_Donnees_Handball.xlsx
+++ b/Base_Donnees_Handball.xlsx
@@ -5,16 +5,19 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\madje\Documents\FeuillesMatchs\Archive\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\madje\Documents\Dashboard Streamlit\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5EDA1F8C-B586-495C-80E6-A1470789DB7A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{70BACB7F-AA7A-4CE3-8CEB-BAF65AC3D782}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="19396" windowHeight="11475" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="2010" yWindow="435" windowWidth="17190" windowHeight="10845" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Données Consolidées" sheetId="1" r:id="rId1"/>
   </sheets>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Données Consolidées'!$A$1:$U$1889</definedName>
+  </definedNames>
   <calcPr calcId="0"/>
 </workbook>
 </file>
@@ -10294,7 +10297,7 @@
         <v>0</v>
       </c>
       <c r="J176">
-        <v>26</v>
+        <v>4</v>
       </c>
       <c r="K176">
         <v>9</v>
@@ -12257,7 +12260,7 @@
         <v>1</v>
       </c>
       <c r="J211">
-        <v>26</v>
+        <v>4</v>
       </c>
       <c r="K211">
         <v>19</v>
@@ -13583,7 +13586,7 @@
         <v>1</v>
       </c>
       <c r="J235">
-        <v>26</v>
+        <v>4</v>
       </c>
       <c r="K235">
         <v>22</v>
@@ -21634,7 +21637,7 @@
         <v>1</v>
       </c>
       <c r="J380">
-        <v>26</v>
+        <v>4</v>
       </c>
       <c r="K380">
         <v>28</v>
@@ -38722,7 +38725,7 @@
         <v>1</v>
       </c>
       <c r="J689">
-        <v>26</v>
+        <v>4</v>
       </c>
       <c r="K689">
         <v>6</v>
@@ -39494,7 +39497,7 @@
         <v>1</v>
       </c>
       <c r="J703">
-        <v>26</v>
+        <v>4</v>
       </c>
       <c r="K703">
         <v>12</v>
@@ -40714,7 +40717,7 @@
         <v>1</v>
       </c>
       <c r="J725">
-        <v>26</v>
+        <v>4</v>
       </c>
       <c r="K725">
         <v>19</v>
@@ -41598,7 +41601,7 @@
         <v>1</v>
       </c>
       <c r="J741">
-        <v>26</v>
+        <v>4</v>
       </c>
       <c r="K741">
         <v>22</v>
@@ -45488,7 +45491,7 @@
         <v>1</v>
       </c>
       <c r="J811">
-        <v>26</v>
+        <v>4</v>
       </c>
       <c r="K811">
         <v>10</v>
@@ -46263,7 +46266,7 @@
         <v>1</v>
       </c>
       <c r="J825">
-        <v>26</v>
+        <v>4</v>
       </c>
       <c r="K825">
         <v>13</v>
@@ -46808,7 +46811,7 @@
         <v>1</v>
       </c>
       <c r="J835">
-        <v>26</v>
+        <v>4</v>
       </c>
       <c r="K835">
         <v>15</v>
@@ -51323,7 +51326,7 @@
         <v>1</v>
       </c>
       <c r="J916">
-        <v>26</v>
+        <v>4</v>
       </c>
       <c r="K916">
         <v>8</v>
@@ -53141,7 +53144,7 @@
         <v>0</v>
       </c>
       <c r="J949">
-        <v>26</v>
+        <v>4</v>
       </c>
       <c r="K949">
         <v>16</v>
@@ -54019,7 +54022,7 @@
         <v>1</v>
       </c>
       <c r="J965">
-        <v>26</v>
+        <v>4</v>
       </c>
       <c r="K965">
         <v>21</v>
@@ -55233,7 +55236,7 @@
         <v>1</v>
       </c>
       <c r="J987">
-        <v>26</v>
+        <v>4</v>
       </c>
       <c r="K987">
         <v>26</v>
@@ -72806,7 +72809,7 @@
         <v>1</v>
       </c>
       <c r="J1306">
-        <v>26</v>
+        <v>4</v>
       </c>
       <c r="K1306">
         <v>12</v>
@@ -73475,7 +73478,7 @@
         <v>1</v>
       </c>
       <c r="J1318">
-        <v>26</v>
+        <v>4</v>
       </c>
       <c r="K1318">
         <v>18</v>
@@ -74480,7 +74483,7 @@
         <v>1</v>
       </c>
       <c r="J1336">
-        <v>26</v>
+        <v>4</v>
       </c>
       <c r="K1336">
         <v>24</v>
@@ -74592,7 +74595,7 @@
         <v>1</v>
       </c>
       <c r="J1338">
-        <v>26</v>
+        <v>4</v>
       </c>
       <c r="K1338">
         <v>25</v>
@@ -75500,7 +75503,7 @@
         <v>1</v>
       </c>
       <c r="J1354">
-        <v>26</v>
+        <v>4</v>
       </c>
       <c r="K1354">
         <v>29</v>
@@ -87327,7 +87330,7 @@
         <v>1</v>
       </c>
       <c r="J1569">
-        <v>26</v>
+        <v>4</v>
       </c>
       <c r="K1569">
         <v>10</v>
@@ -88347,7 +88350,7 @@
         <v>1</v>
       </c>
       <c r="J1587">
-        <v>26</v>
+        <v>4</v>
       </c>
       <c r="K1587">
         <v>17</v>
@@ -90811,7 +90814,7 @@
         <v>1</v>
       </c>
       <c r="J1631">
-        <v>26</v>
+        <v>4</v>
       </c>
       <c r="K1631">
         <v>30</v>
@@ -91250,7 +91253,7 @@
         <v>1</v>
       </c>
       <c r="J1639">
-        <v>26</v>
+        <v>4</v>
       </c>
       <c r="K1639">
         <v>34</v>
@@ -105047,6 +105050,7 @@
       </c>
     </row>
   </sheetData>
+  <autoFilter ref="A1:U1889" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>